--- a/stories/arbres/ATOM-SAN.HYG.002-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, le soleil entre dans la chambre. Émile sent le pain chaud. Maman l'appelle. Émile pousse la porte de la salle de bain. L'eau coule tout doux. Maman tend la brosse bleue. Émile prend la brosse. Un adulte est avec lui. C'est maman. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Émile sent la mousse. Ça goûte un peu la menthe. Parce qu'il brosse le matin, ses dents sont propres. Il rince sa bouche. Il range la brosse. Plus tard, le soir arrive. La lumière est douce. Maman dit : c'est l'heure. Émile revient. Il prend encore la brosse. Maman, l'adulte, se brosse aussi. Matin et soir, c'est pareil. Émile rit un peu. La brosse chatouille. Maman dit : matin et soir, avec un adulte. Émile répète : matin, soir, brosse. Il pose la brosse dans le gobelet. Ses dents brillent.</t>
+          <t>Le matin, le soleil entre dans la chambre. Émile sent le pain chaud. Maman l'appelle. Émile pousse la porte de la salle de bain. L'eau coule tout doux. Maman tend la brosse bleue. Émile prend la brosse. Un adulte est avec lui. C'est maman. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Émile sent la mousse. Ça goûte un peu la menthe. Parce qu'il brosse le matin, ses dents sont propres. Il rince sa bouche. Il range la brosse. Plus tard, le soir arrive. La lumière est douce. C'est l'heure. Émile revient. Il prend encore la brosse. Maman, l'adulte, se brosse aussi. Matin et soir, c'est pareil. Émile rit un peu. La brosse chatouille. Matin et soir, avec un adulte. Émile répète : matin, soir, brosse. Il pose la brosse dans le gobelet. Ses dents brillent.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, le soleil entre dans la chambre. Émile sent le pain chaud. Maman l'appelle. Émile pousse la porte de la salle de bain. L'eau coule tout doux. Maman tend la brosse bleue. Émile prend la brosse. Un adulte est avec lui. C'est maman. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Émile sent la mousse. Ça goûte un peu la menthe. Parce qu'il brosse le matin, ses dents sont propres. Il rince sa bouche. Il range la brosse. Plus tard, le soir arrive. La lumière est douce.
+maman|C'est l'heure.
+narrateur|Émile revient. Il prend encore la brosse. Maman, l'adulte, se brosse aussi. Matin et soir, c'est pareil. Émile rit un peu. La brosse chatouille.
+maman|Matin et soir, avec un adulte.
+narrateur|Émile répète : matin, soir, brosse. Il pose la brosse dans le gobelet. Ses dents brillent.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Émile se brosse les dents. Quand et avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Émile a pris la brosse. Il brosse avec l'adulte. C'est maman. Matin et soir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Émile met son pyjama. Maman éteint la petite lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Émile répète : matin, soir, brosse. Il pose la brosse dans le gobelet. Ses dents brillent.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Émile se brosse les dents. Quand et avec quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1683,7 @@
           <t>narrateur|Émile a pris la brosse. Il brosse avec l'adulte. C'est maman. Matin et soir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Émile met son pyjama. Maman éteint la petite lumière.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.002-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Émile et la brosse du matin</t>
+          <t>La brosse bleue de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le miroir est embué. Le canard jaune attend. Raphaël prend la brosse bleue, matin et soir, avec maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le matin, le soleil entre dans la chambre. Émile sent le pain chaud. Maman l'appelle. Émile pousse la porte de la salle de bain. L'eau coule tout doux. Maman tend la brosse bleue. Émile prend la brosse. Un adulte est avec lui. C'est maman. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Émile sent la mousse. Ça goûte un peu la menthe. Parce qu'il brosse le matin, ses dents sont propres. Il rince sa bouche. Il range la brosse. Plus tard, le soir arrive. La lumière est douce. C'est l'heure. Émile revient. Il prend encore la brosse. Maman, l'adulte, se brosse aussi. Matin et soir, c'est pareil. Émile rit un peu. La brosse chatouille. Matin et soir, avec un adulte. Émile répète : matin, soir, brosse. Il pose la brosse dans le gobelet. Ses dents brillent.</t>
+          <t>Le miroir de la salle de bain est tout blanc. La buée cache le robinet. Un petit canard jaune attend près du savon. Les carreaux sont encore un peu froids. L'odeur du pain chaud vient de la cuisine. Le tapis bleu est doux sous les pieds. Raphaël, tu sens le pain ? Oui, maman. Il est chaud. Le canard a de la buée sur le bec. Il est tout mouillé. En ce moment, Raphaël pousse la porte. L'eau coule, toute tiède. Maman essuie un rond dans le miroir. Voilà ton visage. C'est l'heure de la brosse. Maman tend la brosse bleue. Raphaël prend la brosse. Un adulte est avec lui. C'est maman, près du lavabo. On se brosse ensemble. Moi, l'adulte, je prends la mienne. La brosse va en haut. La brosse va en bas. Ça chatouille. C'est la mousse. La mousse sent la menthe. Ça goûte la menthe. Bravo. Tu prends bien la brosse. Ils se brossent encore un peu. Le matin, on prend la brosse. Avec un adulte. Avec toi. Oui. Avec moi. Raphaël rince sa bouche. L'eau est tiède sur ses doigts. Il pose la brosse dans le gobelet. Le gobelet a des étoiles. Les dents sont propres, ce matin. Elles brillent ? Oui. Un peu. Le canard jaune a séché. Le pain attend dans la cuisine. On va goûter le pain, après. Il est encore chaud ? Oui. Tout doux. Plus tard, la lumière devient douce. La lampe du couloir fait un rond jaune. Le tapis bleu est chaud, maintenant. C'est le soir, Raphaël. C'est l'heure de la brosse. Encore la brosse ? Oui. Matin et soir. Raphaël revient près du lavabo. Il prend encore la brosse bleue. Maman, l'adulte, se brosse aussi. La brosse va en haut. La brosse va en bas. Ça chatouille encore. Matin et soir, avec un adulte. Matin, soir, brosse. Bravo. Tu as fait du bon travail. Raphaël rince sa bouche. Il range la brosse dans le gobelet. Le canard jaune veille près du savon. Tu as fini de ranger la brosse ? Oui, maman. Les dents brillent, ce soir aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,78 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le matin, le soleil entre dans la chambre. Émile sent le pain chaud. Maman l'appelle. Émile pousse la porte de la salle de bain. L'eau coule tout doux. Maman tend la brosse bleue. Émile prend la brosse. Un adulte est avec lui. C'est maman. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Émile sent la mousse. Ça goûte un peu la menthe. Parce qu'il brosse le matin, ses dents sont propres. Il rince sa bouche. Il range la brosse. Plus tard, le soir arrive. La lumière est douce.
-maman|C'est l'heure.
-narrateur|Émile revient. Il prend encore la brosse. Maman, l'adulte, se brosse aussi. Matin et soir, c'est pareil. Émile rit un peu. La brosse chatouille.
+          <t>narrateur|Le miroir de la salle de bain est tout blanc.
+narrateur|La buée cache le robinet.
+narrateur|Un petit canard jaune attend près du savon.
+narrateur|Les carreaux sont encore un peu froids.
+narrateur|L'odeur du pain chaud vient de la cuisine.
+narrateur|Le tapis bleu est doux sous les pieds.
+maman|Raphaël, tu sens le pain ?
+enfant-m|Oui, maman. Il est chaud.
+maman|Le canard a de la buée sur le bec.
+enfant-m|Il est tout mouillé.
+narrateur|En ce moment, Raphaël pousse la porte.
+narrateur|L'eau coule, toute tiède.
+narrateur|Maman essuie un rond dans le miroir.
+maman|Voilà ton visage.
+maman|C'est l'heure de la brosse.
+narrateur|Maman tend la brosse bleue.
+narrateur|Raphaël prend la brosse.
+narrateur|Un adulte est avec lui.
+narrateur|C'est maman, près du lavabo.
+maman|On se brosse ensemble.
+maman|Moi, l'adulte, je prends la mienne.
+narrateur|La brosse va en haut.
+narrateur|La brosse va en bas.
+enfant-m|Ça chatouille.
+maman|C'est la mousse.
+narrateur|La mousse sent la menthe.
+enfant-m|Ça goûte la menthe.
+maman|Bravo. Tu prends bien la brosse.
+narrateur|Ils se brossent encore un peu.
+maman|Le matin, on prend la brosse.
+maman|Avec un adulte.
+enfant-m|Avec toi.
+maman|Oui. Avec moi.
+narrateur|Raphaël rince sa bouche.
+narrateur|L'eau est tiède sur ses doigts.
+narrateur|Il pose la brosse dans le gobelet.
+narrateur|Le gobelet a des étoiles.
+maman|Les dents sont propres, ce matin.
+enfant-m|Elles brillent ?
+maman|Oui. Un peu.
+narrateur|Le canard jaune a séché.
+narrateur|Le pain attend dans la cuisine.
+maman|On va goûter le pain, après.
+enfant-m|Il est encore chaud ?
+maman|Oui. Tout doux.
+narrateur|Plus tard, la lumière devient douce.
+narrateur|La lampe du couloir fait un rond jaune.
+narrateur|Le tapis bleu est chaud, maintenant.
+maman|C'est le soir, Raphaël.
+maman|C'est l'heure de la brosse.
+enfant-m|Encore la brosse ?
+maman|Oui. Matin et soir.
+narrateur|Raphaël revient près du lavabo.
+narrateur|Il prend encore la brosse bleue.
+narrateur|Maman, l'adulte, se brosse aussi.
+narrateur|La brosse va en haut.
+narrateur|La brosse va en bas.
+enfant-m|Ça chatouille encore.
 maman|Matin et soir, avec un adulte.
-narrateur|Émile répète : matin, soir, brosse. Il pose la brosse dans le gobelet. Ses dents brillent.</t>
+enfant-m|Matin, soir, brosse.
+maman|Bravo. Tu as fait du bon travail.
+narrateur|Raphaël rince sa bouche.
+narrateur|Il range la brosse dans le gobelet.
+narrateur|Le canard jaune veille près du savon.
+maman|Tu as fini de ranger la brosse ?
+enfant-m|Oui, maman.
+maman|Les dents brillent, ce soir aussi.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>eau_robinet</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1422,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Émile se brosse les dents. Quand et avec quoi ?</t>
+          <t>Raphaël se brosse les dents. Quand et avec quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,10 +1582,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Émile se brosse les dents. Quand et avec quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël se brosse les dents.
+narrateur|Quand et avec quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,7 +1610,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Émile a pris la brosse. Il brosse avec l'adulte. C'est maman. Matin et soir.</t>
+          <t>Raphaël a pris la brosse. Il brosse avec l'adulte. C'est maman. Matin et soir. Tu as pris la brosse ? Oui. Matin et soir. Avec un adulte. Bravo. C'est du bon travail. Le canard jaune est tout sec.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,10 +1754,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Émile a pris la brosse. Il brosse avec l'adulte. C'est maman. Matin et soir.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël a pris la brosse.
+narrateur|Il brosse avec l'adulte.
+narrateur|C'est maman.
+narrateur|Matin et soir.
+maman|Tu as pris la brosse ?
+enfant-m|Oui. Matin et soir.
+maman|Avec un adulte. Bravo.
+maman|C'est du bon travail.
+narrateur|Le canard jaune est tout sec.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,7 +1789,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Émile met son pyjama. Maman éteint la petite lumière.</t>
+          <t>Raphaël met son pyjama à rayures. Le tissu est doux sur les bras. Tu veux la petite lumière ? Oui. Tout doux. Maman baisse la lampe. Le canard reste près du savon. Dors bien, Raphaël. Bonne nuit, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1925,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Émile met son pyjama. Maman éteint la petite lumière.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Raphaël met son pyjama à rayures.
+narrateur|Le tissu est doux sur les bras.
+maman|Tu veux la petite lumière ?
+enfant-m|Oui. Tout doux.
+narrateur|Maman baisse la lampe.
+narrateur|Le canard reste près du savon.
+maman|Dors bien, Raphaël.
+enfant-m|Bonne nuit, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Matin et soir, la brosse. Avec un adulte. Bravo. Le gobelet garde la brosse bleue. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2099,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Matin et soir, la brosse.
+maman|Avec un adulte. Bravo.
+narrateur|Le gobelet garde la brosse bleue.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le miroir de la salle de bain est tout blanc. La buée cache le robinet. Un petit canard jaune attend près du savon. Les carreaux sont encore un peu froids. L'odeur du pain chaud vient de la cuisine. Le tapis bleu est doux sous les pieds. Raphaël, tu sens le pain ? Oui, maman. Il est chaud. Le canard a de la buée sur le bec. Il est tout mouillé. En ce moment, Raphaël pousse la porte. L'eau coule, toute tiède. Maman essuie un rond dans le miroir. Voilà ton visage. C'est l'heure de la brosse. Maman tend la brosse bleue. Raphaël prend la brosse. Un adulte est avec lui. C'est maman, près du lavabo. On se brosse ensemble. Moi, l'adulte, je prends la mienne. La brosse va en haut. La brosse va en bas. Ça chatouille. C'est la mousse. La mousse sent la menthe. Ça goûte la menthe. Bravo. Tu prends bien la brosse. Ils se brossent encore un peu. Le matin, on prend la brosse. Avec un adulte. Avec toi. Oui. Avec moi. Raphaël rince sa bouche. L'eau est tiède sur ses doigts. Il pose la brosse dans le gobelet. Le gobelet a des étoiles. Les dents sont propres, ce matin. Elles brillent ? Oui. Un peu. Le canard jaune a séché. Le pain attend dans la cuisine. On va goûter le pain, après. Il est encore chaud ? Oui. Tout doux. Plus tard, la lumière devient douce. La lampe du couloir fait un rond jaune. Le tapis bleu est chaud, maintenant. C'est le soir, Raphaël. C'est l'heure de la brosse. Encore la brosse ? Oui. Matin et soir. Raphaël revient près du lavabo. Il prend encore la brosse bleue. Maman, l'adulte, se brosse aussi. La brosse va en haut. La brosse va en bas. Ça chatouille encore. Matin et soir, avec un adulte. Matin, soir, brosse. Bravo. Tu as fait du bon travail. Raphaël rince sa bouche. Il range la brosse dans le gobelet. Le canard jaune veille près du savon. Tu as fini de ranger la brosse ? Oui, maman. Les dents brillent, ce soir aussi.</t>
+          <t>Le miroir de la salle de bain est tout blanc. La buée cache le robinet. Un petit canard jaune attend près du savon. Les carreaux sont encore un peu froids. L'odeur du pain chaud vient de la cuisine. Le tapis bleu est doux sous les pieds. Raphaël, tu sens le pain ? Oui, maman. Il est chaud. Le canard a de la buée sur le bec. Il est tout mouillé. En ce moment, Raphaël pousse la porte. L'eau coule, toute tiède. Maman essuie un rond dans le miroir. Voilà ton visage. C'est l'heure de la brosse. Maman tend la brosse bleue. Raphaël prend la brosse. Un adulte est avec lui. C'est maman, près du lavabo. On se brosse ensemble. Moi, l'adulte, je prends la mienne. La brosse va en haut. La brosse va en bas. Ça chatouille. C'est la mousse. La mousse sent la menthe. Ça goûte la menthe. Bravo. Tu prends bien la brosse. Ils se brossent encore un peu. Le matin, on prend la brosse. Avec un adulte. Avec toi. Oui. Avec moi. Raphaël rince sa bouche. L'eau est tiède sur ses doigts. Il pose la brosse dans le gobelet. Le gobelet a des étoiles. Les dents sont propres, ce matin. Elles brillent ? Oui. Un peu. Le canard jaune a séché. Le pain attend dans la cuisine. On va goûter le pain, après. Il est encore chaud ? Oui. Tout doux. Plus tard, la lumière devient douce. La lampe du couloir fait un rond jaune. Le tapis bleu est chaud, maintenant. C'est le soir, Raphaël. C'est l'heure de la brosse. Encore la brosse ? Oui. Matin et soir. Raphaël revient près du lavabo. Il prend encore la brosse bleue. Maman, l'adulte, se brosse aussi. La brosse va en haut. La brosse va en bas. Ça chatouille encore. Matin et soir, avec un adulte. Matin, soir, brosse. Raphaël rince sa bouche. Il range la brosse dans le gobelet. Le canard jaune veille près du savon. Tu as fini de ranger la brosse ? Oui, maman. Les dents brillent, ce soir aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;matin&lt;/emphasis&gt;, le soleil entre dans la chambre. Émile sent le pain chaud. Maman l'appelle. Émile pousse la porte de la salle de bain. L'eau coule tout doux. Maman tend la brosse bleue. Émile prend la brosse. Un adulte est avec lui. C'est maman. Ils se brossent ensemble. La brosse va en haut. La brosse va en bas. Émile sent la mousse. Ça goûte un peu la menthe. Parce qu'il brosse le matin, ses dents sont propres. Il rince sa bouche. Il range la brosse. Plus tard, le soir arrive. La lumière est douce. Maman dit : c'est l'heure. Émile revient. Il prend encore la brosse. Maman, l'adulte, se brosse aussi. Matin et soir, c'est pareil. Émile rit un peu. La brosse chatouille. Maman dit : matin et soir, avec un adulte. Émile répète : matin, soir, brosse. Il pose la brosse dans le gobelet. Ses dents brillent.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le miroir de la salle de bain est tout blanc. La buée cache le robinet. Un petit canard jaune attend près du savon. Les carreaux sont encore un peu froids. L'odeur du pain chaud vient de la cuisine. Le tapis bleu est doux sous les pieds. Raphaël, tu sens le pain ? Oui, maman. Il est chaud. Le canard a de la buée sur le bec. Il est tout mouillé. En ce moment, Raphaël pousse la porte. L'eau coule, toute tiède. Maman essuie un rond dans le miroir. Voilà ton visage. C'est l'heure de la brosse. Maman tend la brosse bleue. Raphaël prend la brosse. Un adulte est avec lui. C'est maman, près du lavabo. On se brosse ensemble. Moi, l'adulte, je prends la mienne. La brosse va en haut. La brosse va en bas. Ça chatouille. C'est la mousse. La mousse sent la menthe. Ça goûte la menthe. Bravo. Tu prends bien la brosse. Ils se brossent encore un peu. Le matin, on prend la brosse. Avec un adulte. Avec toi. Oui. Avec moi. Raphaël rince sa bouche. L'eau est tiède sur ses doigts. Il pose la brosse dans le gobelet. Le gobelet a des étoiles. Les dents sont propres, ce matin. Elles brillent ? Oui. Un peu. Le canard jaune a séché. Le pain attend dans la cuisine. On va goûter le pain, après. Il est encore chaud ? Oui. Tout doux. Plus tard, la lumière devient douce. La lampe du couloir fait un rond jaune. Le tapis bleu est chaud, maintenant. C'est le soir, Raphaël. C'est l'heure de la brosse. Encore la brosse ? Oui. Matin et soir. Raphaël revient près du lavabo. Il prend encore la brosse bleue. Maman, l'adulte, se brosse aussi. La brosse va en haut. La brosse va en bas. Ça chatouille encore. Matin et soir, avec un adulte. Matin, soir, brosse. Raphaël rince sa bouche. Il range la brosse dans le gobelet. Le canard jaune veille près du savon. Tu as fini de ranger la brosse ? Oui, maman. Les dents brillent, ce soir aussi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1384,7 +1384,6 @@
 enfant-m|Ça chatouille encore.
 maman|Matin et soir, avec un adulte.
 enfant-m|Matin, soir, brosse.
-maman|Bravo. Tu as fait du bon travail.
 narrateur|Raphaël rince sa bouche.
 narrateur|Il range la brosse dans le gobelet.
 narrateur|Le canard jaune veille près du savon.
@@ -1427,7 +1426,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Émile se &lt;emphasis level="moderate"&gt;brosse&lt;/emphasis&gt; les dents. Quand et avec quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël se brosse les dents. Quand et avec quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1610,12 +1609,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a pris la brosse. Il brosse avec l'adulte. C'est maman. Matin et soir. Tu as pris la brosse ? Oui. Matin et soir. Avec un adulte. Bravo. C'est du bon travail. Le canard jaune est tout sec.</t>
+          <t>Raphaël a pris la brosse. Il brosse avec l'adulte. C'est maman. Matin et soir. Tu as pris la brosse ? Oui. Matin et soir. Avec un adulte. Bravo. Le canard jaune est tout sec.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Émile a pris la brosse. Il brosse avec l'adulte. C'est maman. &lt;emphasis level="moderate"&gt;matin&lt;/emphasis&gt; et soir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a pris la brosse. Il brosse avec l'adulte. C'est maman. Matin et soir. Tu as pris la brosse ? Oui. Matin et soir. Avec un adulte. Bravo. Le canard jaune est tout sec.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1761,7 +1760,6 @@
 maman|Tu as pris la brosse ?
 enfant-m|Oui. Matin et soir.
 maman|Avec un adulte. Bravo.
-maman|C'est du bon travail.
 narrateur|Le canard jaune est tout sec.</t>
         </is>
       </c>
@@ -1794,7 +1792,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Émile met son pyjama. Maman éteint la petite lumière.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël met son pyjama à rayures. Le tissu est doux sur les bras. Tu veux la petite lumière ? Oui. Tout doux. Maman baisse la lampe. Le canard reste près du savon. Dors bien, Raphaël. Bonne nuit, maman.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1959,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Matin et soir, la brosse. Avec un adulte. Bravo. Le gobelet garde la brosse bleue. L'histoire est finie.</t>
+          <t>Matin et soir, la brosse. Avec un adulte. Bravo. Le gobelet garde la brosse bleue.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Matin et soir, la brosse. Avec un adulte. Bravo. Le gobelet garde la brosse bleue.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,8 +2099,7 @@
         <is>
           <t>enfant-m|Matin et soir, la brosse.
 maman|Avec un adulte. Bravo.
-narrateur|Le gobelet garde la brosse bleue.
-narrateur|L'histoire est finie.</t>
+narrateur|Le gobelet garde la brosse bleue.</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2165,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-04.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salle de bain</t>
+          <t>salle de bain, miroir embué, canard jaune</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Émile, maman</t>
+          <t>Raphaël, maman</t>
         </is>
       </c>
     </row>
